--- a/hiring_companies_2026-10-27.xlsx
+++ b/hiring_companies_2026-10-27.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDM Technology</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,22 +492,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C#/.NET Backend Software Engineer II</t>
+          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2794576919690955576</t>
+          <t>https://jooble.org/jdp/6022615829687629192</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CDM+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDM Technology</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C#/.NET Backend Software Engineer II</t>
+          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2794576919690955576</t>
+          <t>https://jooble.org/jdp/-1105644686765869484</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CDM+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDM Technology</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C#/.NET Backend Software Engineer II</t>
+          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2794576919690955576</t>
+          <t>https://jooble.org/jdp/-1105644686765869484</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CDM+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDM Technology</t>
+          <t>ADT Worldwide</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -633,22 +633,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C#/.NET Backend Software Engineer II</t>
+          <t>Senior Embedded Software Engineer - Linux/Firmware</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2794576919690955576</t>
+          <t>https://jooble.org/jdp/-8369703360125224661</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CDM+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ADT+Worldwide</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDM Technology</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,22 +680,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C#/.NET Backend Software Engineer II</t>
+          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2794576919690955576</t>
+          <t>https://jooble.org/jdp/-1105644686765869484</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CDM+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDM Technology</t>
+          <t>ADT Worldwide</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,22 +727,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C#/.NET Backend Software Engineer II</t>
+          <t>Senior Embedded Software Engineer - Linux/Firmware</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2794576919690955576</t>
+          <t>https://jooble.org/jdp/-8369703360125224661</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CDM+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ADT+Worldwide</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Optomi</t>
+          <t>True Crime Story911 Media Group (TCS911 Media)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer - Remote</t>
+          <t>Social Media Intern — Unpaid Internship</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7137718470254137129</t>
+          <t>https://jooble.org/jdp/-8309850523407023670</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optomi</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Optomi</t>
+          <t>True Crime Story911 Media Group (TCS911 Media)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer - Remote</t>
+          <t>Social Media Intern — Unpaid Internship</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7137718470254137129</t>
+          <t>https://jooble.org/jdp/-8309850523407023670</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optomi</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Optomi</t>
+          <t>True Crime Story911 Media Group (TCS911 Media)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -868,22 +868,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer - Remote</t>
+          <t>Social Media Intern — Unpaid Internship</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7137718470254137129</t>
+          <t>https://jooble.org/jdp/-8309850523407023670</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optomi</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Optomi</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,22 +915,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer - Remote</t>
+          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7137718470254137129</t>
+          <t>https://jooble.org/jdp/6022615829687629192</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optomi</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>True Crime Story911 Media Group (TCS911 Media)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Social Media Intern — Unpaid Internship</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5910436290900339127</t>
+          <t>https://jooble.org/jdp/-8309850523407023670</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCLTech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,22 +1009,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5910436290900339127</t>
+          <t>https://jooble.org/jdp/6022615829687629192</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCLTech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Jeevanvijeta</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5910436290900339127</t>
+          <t>https://jooble.org/jdp/-4662911160754589545</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCLTech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Cypress Group</t>
+          <t>Jeevanvijeta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Database Platform Engineer</t>
+          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2692236813534609835</t>
+          <t>https://jooble.org/jdp/-4662911160754589545</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cypress+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Jeevanvijeta</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5910436290900339127</t>
+          <t>https://jooble.org/jdp/-4662911160754589545</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCLTech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The Cypress Group</t>
+          <t>True Crime Story911 Media Group (TCS911 Media)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Database Platform Engineer</t>
+          <t>Social Media Intern — Unpaid Internship</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2692236813534609835</t>
+          <t>https://jooble.org/jdp/-8309850523407023670</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cypress+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Optomi</t>
+          <t>Jeevanvijeta</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer - Remote</t>
+          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7137718470254137129</t>
+          <t>https://jooble.org/jdp/-4662911160754589545</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optomi</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Optomi</t>
+          <t>True Crime Story911 Media Group (TCS911 Media)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer - Remote</t>
+          <t>Social Media Intern — Unpaid Internship</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7137718470254137129</t>
+          <t>https://jooble.org/jdp/-8309850523407023670</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optomi</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>The Cypress Group</t>
+          <t>Foursets</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Database Platform Engineer</t>
+          <t>Remote Web Designer for Growth-Driven Websites</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2692236813534609835</t>
+          <t>https://jooble.org/jdp/-2769769183989676819</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cypress+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Foursets</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,22 +1385,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Remote Web Designer for Growth-Driven Websites</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5910436290900339127</t>
+          <t>https://jooble.org/jdp/-2769769183989676819</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCLTech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The Cypress Group</t>
+          <t>Foursets</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,22 +1432,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Database Platform Engineer</t>
+          <t>Remote Web Designer for Growth-Driven Websites</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2692236813534609835</t>
+          <t>https://jooble.org/jdp/-2769769183989676819</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cypress+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Jeevanvijeta</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5910436290900339127</t>
+          <t>https://jooble.org/jdp/-4662911160754589545</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCLTech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The Cypress Group</t>
+          <t>Foursets</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1526,22 +1526,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Database Platform Engineer</t>
+          <t>Remote Web Designer for Growth-Driven Websites</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2692236813534609835</t>
+          <t>https://jooble.org/jdp/-2769769183989676819</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cypress+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>The Cypress Group</t>
+          <t>Jeevanvijeta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1573,22 +1573,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Database Platform Engineer</t>
+          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2692236813534609835</t>
+          <t>https://jooble.org/jdp/-4662911160754589545</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cypress+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cartessa Aesthetics</t>
+          <t>W001 Old Republic Title Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Inside Sales Specialist</t>
+          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/439028349999764929</t>
+          <t>https://jooble.org/jdp/-1616134175009281857</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cartessa+Aesthetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cartessa Aesthetics</t>
+          <t>Stratford Davis LLC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Inside Sales Specialist</t>
+          <t>Solutions Sales Representative - Remote</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/439028349999764929</t>
+          <t>https://jooble.org/jdp/-2441186257857731571</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cartessa+Aesthetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cartessa Aesthetics</t>
+          <t>Stratford Davis LLC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Inside Sales Specialist</t>
+          <t>Solutions Sales Representative - Remote</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/439028349999764929</t>
+          <t>https://jooble.org/jdp/-2441186257857731571</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cartessa+Aesthetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cartessa Aesthetics</t>
+          <t>Foursets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Inside Sales Specialist</t>
+          <t>Remote Web Designer for Growth-Driven Websites</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/439028349999764929</t>
+          <t>https://jooble.org/jdp/-2769769183989676819</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cartessa+Aesthetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cartessa Aesthetics</t>
+          <t>Stratford Davis LLC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Inside Sales Specialist</t>
+          <t>Solutions Sales Representative - Remote</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/439028349999764929</t>
+          <t>https://jooble.org/jdp/3125583918601785829</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cartessa+Aesthetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cartessa Aesthetics</t>
+          <t>Foursets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1855,22 +1855,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Inside Sales Specialist</t>
+          <t>Remote Web Designer for Growth-Driven Websites</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/439028349999764929</t>
+          <t>https://jooble.org/jdp/-2769769183989676819</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cartessa+Aesthetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IBSA USA</t>
+          <t>Hire Latam LLC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Specialty Sales Representative - Memphis, TN</t>
+          <t>Remote Homebuyer Sales Specialist</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3564805766070931866</t>
+          <t>https://jooble.org/jdp/9048875994745794016</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IBSA+USA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,7 +1934,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IBSA USA</t>
+          <t>W001 Old Republic Title Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Specialty Sales Representative - Asheville, NC</t>
+          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8441160516099773319</t>
+          <t>https://jooble.org/jdp/-1616134175009281857</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IBSA+USA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IBSA USA</t>
+          <t>W001 Old Republic Title Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Specialty Sales Representative - Asheville, NC</t>
+          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8441160516099773319</t>
+          <t>https://jooble.org/jdp/-1616134175009281857</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IBSA+USA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IBSA USA</t>
+          <t>W001 Old Republic Title Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Specialty Sales Representative - Memphis, TN</t>
+          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3564805766070931866</t>
+          <t>https://jooble.org/jdp/-1616134175009281857</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IBSA+USA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IBSA USA</t>
+          <t>W001 Old Republic Title Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Specialty Sales Representative - Asheville, NC</t>
+          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8441160516099773319</t>
+          <t>https://jooble.org/jdp/-1616134175009281857</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IBSA+USA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IBSA USA</t>
+          <t>W001 Old Republic Title Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Specialty Sales Representative - Asheville, NC</t>
+          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8441160516099773319</t>
+          <t>https://jooble.org/jdp/-1616134175009281857</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IBSA+USA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>THE CHAMPION COMPANY</t>
+          <t>Stratford Davis LLC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Regional Inside Sales Representative</t>
+          <t>Solutions Sales Representative - Remote</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6157658570341447342</t>
+          <t>https://jooble.org/jdp/4238151110188515191</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=THE+CHAMPION+COMPANY</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>THE CHAMPION COMPANY</t>
+          <t>Hire Latam LLC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Regional Inside Sales Representative</t>
+          <t>Remote Homebuyer Sales Specialist</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6157658570341447342</t>
+          <t>https://jooble.org/jdp/9048875994745794016</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=THE+CHAMPION+COMPANY</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,7 +2263,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>THE CHAMPION COMPANY</t>
+          <t>Hire Latam LLC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Regional Inside Sales Representative</t>
+          <t>Remote Homebuyer Sales Specialist</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6157658570341447342</t>
+          <t>https://jooble.org/jdp/9048875994745794016</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=THE+CHAMPION+COMPANY</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>THE CHAMPION COMPANY</t>
+          <t>Hire Latam LLC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Regional Inside Sales Representative</t>
+          <t>Remote Homebuyer Sales Specialist</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6157658570341447342</t>
+          <t>https://jooble.org/jdp/9048875994745794016</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=THE+CHAMPION+COMPANY</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>THE CHAMPION COMPANY</t>
+          <t>Hire Latam LLC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Regional Inside Sales Representative</t>
+          <t>Remote Homebuyer Sales Specialist</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6157658570341447342</t>
+          <t>https://jooble.org/jdp/9048875994745794016</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=THE+CHAMPION+COMPANY</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>THE CHAMPION COMPANY</t>
+          <t>Hire Latam LLC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Regional Inside Sales Representative</t>
+          <t>Remote Homebuyer Sales Specialist</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6157658570341447342</t>
+          <t>https://jooble.org/jdp/9048875994745794016</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=THE+CHAMPION+COMPANY</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>The Cooper Group LLC</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Remote Sales Agent, Industry Experience Preferred</t>
+          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-168096558815537993</t>
+          <t>https://jooble.org/jdp/2795760864589697441</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cooper+Group+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>The Cooper Group LLC</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Remote Sales Agent, Industry Experience Preferred</t>
+          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-168096558815537993</t>
+          <t>https://jooble.org/jdp/2795760864589697441</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cooper+Group+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>The Cooper Group LLC</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remote Sales Agent, Industry Experience Preferred</t>
+          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-168096558815537993</t>
+          <t>https://jooble.org/jdp/2795760864589697441</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cooper+Group+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>The Cooper Group LLC</t>
+          <t>Stratford Davis LLC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Remote Sales Agent, Industry Experience Preferred</t>
+          <t>Solutions Sales Representative - Remote</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-168096558815537993</t>
+          <t>https://jooble.org/jdp/4238151110188515191</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cooper+Group+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>The Cooper Group LLC</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Remote Sales Agent, Industry Experience Preferred</t>
+          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-168096558815537993</t>
+          <t>https://jooble.org/jdp/2795760864589697441</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cooper+Group+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The Cooper Group LLC</t>
+          <t>Stratford Davis LLC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Remote Sales Agent, Industry Experience Preferred</t>
+          <t>Solutions Sales Representative - Remote</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-168096558815537993</t>
+          <t>https://jooble.org/jdp/4238151110188515191</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Cooper+Group+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Joseph Michaels International</t>
+          <t>Diouf.co</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Oracle Developer - Cloud / Fusion OFSC, WAM, WACS and/or CCS</t>
+          <t>Sales Director</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4402778224602856976</t>
+          <t>https://jooble.org/jdp/6111742176005590816</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Joseph+Michaels+International</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Diouf.co</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Joseph Michaels International</t>
+          <t>Flockx</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Oracle Developer - Cloud / Fusion OFSC, WAM, WACS and/or CCS</t>
+          <t>Junior Video Creator &amp; Editor</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4402778224602856976</t>
+          <t>https://jooble.org/jdp/1305495357848906713</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Joseph+Michaels+International</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Flockx</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">

--- a/hiring_companies_2026-10-27.xlsx
+++ b/hiring_companies_2026-10-27.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Comdal Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,12 +492,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
+          <t>Web Graphic Designer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6022615829687629192</t>
+          <t>https://jooble.org/jdp/-1316669408751818157</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Comdal+Limited</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Comdal Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
+          <t>Web Graphic Designer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1105644686765869484</t>
+          <t>https://jooble.org/jdp/-1316669408751818157</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Comdal+Limited</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Comdal Limited</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
+          <t>Web Graphic Designer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1105644686765869484</t>
+          <t>https://jooble.org/jdp/-1316669408751818157</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Comdal+Limited</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADT Worldwide</t>
+          <t>Comdal Limited</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Embedded Software Engineer - Linux/Firmware</t>
+          <t>Web Graphic Designer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8369703360125224661</t>
+          <t>https://jooble.org/jdp/-1316669408751818157</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ADT+Worldwide</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Comdal+Limited</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Comdal Limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
+          <t>Web Graphic Designer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1105644686765869484</t>
+          <t>https://jooble.org/jdp/-1316669408751818157</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Comdal+Limited</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADT Worldwide</t>
+          <t>Comdal Limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Embedded Software Engineer - Linux/Firmware</t>
+          <t>Web Graphic Designer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8369703360125224661</t>
+          <t>https://jooble.org/jdp/-1316669408751818157</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ADT+Worldwide</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Comdal+Limited</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>True Crime Story911 Media Group (TCS911 Media)</t>
+          <t>Aglow Sports Konsult</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Social Media Intern — Unpaid Internship</t>
+          <t>Remote Web Designer - UX-Driven &amp; Responsive Design</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8309850523407023670</t>
+          <t>https://jooble.org/jdp/5977439848397640269</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aglow+Sports+Konsult</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>True Crime Story911 Media Group (TCS911 Media)</t>
+          <t>Aglow Sports Konsult</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Social Media Intern — Unpaid Internship</t>
+          <t>Remote Web Designer - UX-Driven &amp; Responsive Design</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8309850523407023670</t>
+          <t>https://jooble.org/jdp/5977439848397640269</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aglow+Sports+Konsult</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>True Crime Story911 Media Group (TCS911 Media)</t>
+          <t>Aglow Sports Konsult</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Social Media Intern — Unpaid Internship</t>
+          <t>Remote Web Designer - UX-Driven &amp; Responsive Design</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8309850523407023670</t>
+          <t>https://jooble.org/jdp/5977439848397640269</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aglow+Sports+Konsult</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Aglow Sports Konsult</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
+          <t>Remote Web Designer - UX-Driven &amp; Responsive Design</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6022615829687629192</t>
+          <t>https://jooble.org/jdp/5977439848397640269</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aglow+Sports+Konsult</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>True Crime Story911 Media Group (TCS911 Media)</t>
+          <t>Aglow Sports Konsult</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Social Media Intern — Unpaid Internship</t>
+          <t>Remote Web Designer - UX-Driven &amp; Responsive Design</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8309850523407023670</t>
+          <t>https://jooble.org/jdp/5977439848397640269</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aglow+Sports+Konsult</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Aglow Sports Konsult</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ad Creative Strategist (Freelance) | Director, Newsletter &amp; Email Marketing | Performance Marketing Manager | Senior MongoDB Database Platform Engineer | Social Media Specialist | Technical Marketing,</t>
+          <t>Remote Web Designer - UX-Driven &amp; Responsive Design</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6022615829687629192</t>
+          <t>https://jooble.org/jdp/5977439848397640269</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Aglow+Sports+Konsult</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jeevanvijeta</t>
+          <t>Active Minds</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
+          <t>Spring 2027 Digital Media Intern</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4662911160754589545</t>
+          <t>https://jooble.org/jdp/-1704827260281952643</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Active+Minds</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jeevanvijeta</t>
+          <t>Active Minds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
+          <t>Spring 2027 Digital Media Intern</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4662911160754589545</t>
+          <t>https://jooble.org/jdp/5423433256171546033</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Active+Minds</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jeevanvijeta</t>
+          <t>Old Republic Title</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
+          <t>Assistant Video Editor (Part-time)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4662911160754589545</t>
+          <t>https://jooble.org/jdp/5300553821400255541</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Old+Republic+Title</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>True Crime Story911 Media Group (TCS911 Media)</t>
+          <t>Active Minds</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Social Media Intern — Unpaid Internship</t>
+          <t>Spring 2027 Digital Media Intern</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8309850523407023670</t>
+          <t>https://jooble.org/jdp/5423433256171546033</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Active+Minds</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jeevanvijeta</t>
+          <t>Active Minds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
+          <t>Spring 2027 Digital Media Intern</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4662911160754589545</t>
+          <t>https://jooble.org/jdp/5423433256171546033</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Active+Minds</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>True Crime Story911 Media Group (TCS911 Media)</t>
+          <t>Active Minds</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Social Media Intern — Unpaid Internship</t>
+          <t>Spring 2027 Digital Media Intern</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8309850523407023670</t>
+          <t>https://jooble.org/jdp/-1704827260281952643</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True+Crime+Story911+Media+Group+%28TCS911+Media%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Active+Minds</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foursets</t>
+          <t>Old Republic Title</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Remote Web Designer for Growth-Driven Websites</t>
+          <t>Assistant Video Editor (Part-time)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2769769183989676819</t>
+          <t>https://jooble.org/jdp/5300553821400255541</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Old+Republic+Title</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Foursets</t>
+          <t>Old Republic Title</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Remote Web Designer for Growth-Driven Websites</t>
+          <t>Assistant Video Editor (Part-time)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2769769183989676819</t>
+          <t>https://jooble.org/jdp/2774694335355831177</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Old+Republic+Title</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Foursets</t>
+          <t>Active Minds</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Remote Web Designer for Growth-Driven Websites</t>
+          <t>Spring 2027 Digital Media Intern</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2769769183989676819</t>
+          <t>https://jooble.org/jdp/5423433256171546033</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Active+Minds</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jeevanvijeta</t>
+          <t>Old Republic Title</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
+          <t>Assistant Video Editor (Part-time)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4662911160754589545</t>
+          <t>https://jooble.org/jdp/2774694335355831177</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Old+Republic+Title</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Foursets</t>
+          <t>Old Republic Title</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Remote Web Designer for Growth-Driven Websites</t>
+          <t>Assistant Video Editor (Part-time)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2769769183989676819</t>
+          <t>https://jooble.org/jdp/2774694335355831177</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Old+Republic+Title</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jeevanvijeta</t>
+          <t>Old Republic Title</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI Video Editor &amp; Social Media Creator - Remote</t>
+          <t>Assistant Video Editor (Part-time)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4662911160754589545</t>
+          <t>https://jooble.org/jdp/5300553821400255541</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeevanvijeta</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Old+Republic+Title</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>W001 Old Republic Title Holding Company, Inc.</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1616134175009281857</t>
+          <t>https://jooble.org/jdp/-4693506583660694181</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+Washington</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stratford Davis LLC</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Solutions Sales Representative - Remote</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2441186257857731571</t>
+          <t>https://jooble.org/jdp/-4693506583660694181</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+Washington</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stratford Davis LLC</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Solutions Sales Representative - Remote</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2441186257857731571</t>
+          <t>https://jooble.org/jdp/-4693506583660694181</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+Washington</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Foursets</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Remote Web Designer for Growth-Driven Websites</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2769769183989676819</t>
+          <t>https://jooble.org/jdp/-4693506583660694181</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+Washington</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Stratford Davis LLC</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Solutions Sales Representative - Remote</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3125583918601785829</t>
+          <t>https://jooble.org/jdp/-4693506583660694181</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+Washington</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Foursets</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Remote Web Designer for Growth-Driven Websites</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2769769183989676819</t>
+          <t>https://jooble.org/jdp/-4693506583660694181</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foursets</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+Washington</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hire Latam LLC</t>
+          <t>The Daily Pour</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Remote Homebuyer Sales Specialist</t>
+          <t>Sales Associate, Digital Partnerships</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9048875994745794016</t>
+          <t>https://jooble.org/jdp/-6749005925761224616</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Daily+Pour</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,7 +1934,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>W001 Old Republic Title Holding Company, Inc.</t>
+          <t>The Daily Pour</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
+          <t>Sales Associate, Digital Partnerships</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1616134175009281857</t>
+          <t>https://jooble.org/jdp/-6749005925761224616</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Daily+Pour</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>W001 Old Republic Title Holding Company, Inc.</t>
+          <t>The Daily Pour</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
+          <t>Sales Associate, Digital Partnerships</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1616134175009281857</t>
+          <t>https://jooble.org/jdp/-6749005925761224616</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Daily+Pour</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>W001 Old Republic Title Holding Company, Inc.</t>
+          <t>The Daily Pour</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
+          <t>Sales Associate, Digital Partnerships</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1616134175009281857</t>
+          <t>https://jooble.org/jdp/-6749005925761224616</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Daily+Pour</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>W001 Old Republic Title Holding Company, Inc.</t>
+          <t>The Daily Pour</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
+          <t>Sales Associate, Digital Partnerships</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1616134175009281857</t>
+          <t>https://jooble.org/jdp/-6749005925761224616</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Daily+Pour</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>W001 Old Republic Title Holding Company, Inc.</t>
+          <t>The Daily Pour</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Remote Part-Time Assistant Video Editor - Social Media</t>
+          <t>Sales Associate, Digital Partnerships</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1616134175009281857</t>
+          <t>https://jooble.org/jdp/-6749005925761224616</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=W001+Old+Republic+Title+Holding+Company%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Daily+Pour</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Stratford Davis LLC</t>
+          <t>Carolina Waterfowl Rescue</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Solutions Sales Representative - Remote</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4238151110188515191</t>
+          <t>https://jooble.org/jdp/-4267740989374043661</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Carolina+Waterfowl+Rescue</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hire Latam LLC</t>
+          <t>nothing else</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Remote Homebuyer Sales Specialist</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9048875994745794016</t>
+          <t>https://jooble.org/jdp/7045941281716874648</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=nothing+else</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,7 +2263,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hire Latam LLC</t>
+          <t>nothing else</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Remote Homebuyer Sales Specialist</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9048875994745794016</t>
+          <t>https://jooble.org/jdp/7045941281716874648</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=nothing+else</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hire Latam LLC</t>
+          <t>nothing else</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Remote Homebuyer Sales Specialist</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9048875994745794016</t>
+          <t>https://jooble.org/jdp/7045941281716874648</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=nothing+else</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hire Latam LLC</t>
+          <t>nothing else</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Remote Homebuyer Sales Specialist</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9048875994745794016</t>
+          <t>https://jooble.org/jdp/7045941281716874648</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=nothing+else</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hire Latam LLC</t>
+          <t>Carolina Waterfowl Rescue</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Remote Homebuyer Sales Specialist</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9048875994745794016</t>
+          <t>https://jooble.org/jdp/-4267740989374043661</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hire+Latam+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Carolina+Waterfowl+Rescue</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>nothing else</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2795760864589697441</t>
+          <t>https://jooble.org/jdp/7045941281716874648</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=nothing+else</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Carolina Waterfowl Rescue</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2795760864589697441</t>
+          <t>https://jooble.org/jdp/-4267740989374043661</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Carolina+Waterfowl+Rescue</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Carolina Waterfowl Rescue</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2795760864589697441</t>
+          <t>https://jooble.org/jdp/-4267740989374043661</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Carolina+Waterfowl+Rescue</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Stratford Davis LLC</t>
+          <t>Carolina Waterfowl Rescue</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Solutions Sales Representative - Remote</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4238151110188515191</t>
+          <t>https://jooble.org/jdp/-4267740989374043661</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Carolina+Waterfowl+Rescue</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Carolina Waterfowl Rescue</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SLED Storage Sales Specialist - MA | Storage Sales Specialist</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2795760864589697441</t>
+          <t>https://jooble.org/jdp/-4267740989374043661</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hewlett+Packard+Enterprise</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Carolina+Waterfowl+Rescue</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stratford Davis LLC</t>
+          <t>nothing else</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Solutions Sales Representative - Remote</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4238151110188515191</t>
+          <t>https://jooble.org/jdp/7045941281716874648</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Stratford+Davis+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=nothing+else</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Diouf.co</t>
+          <t>Contrarian Thinking</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sales Director</t>
+          <t>Remote Short-Form Video Editor for Viral Clips</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6111742176005590816</t>
+          <t>https://jooble.org/jdp/3426451598249722148</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Diouf.co</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Contrarian+Thinking</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Flockx</t>
+          <t>Contrarian Thinking</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Junior Video Creator &amp; Editor</t>
+          <t>Remote Short-Form Video Editor for Viral Clips</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1305495357848906713</t>
+          <t>https://jooble.org/jdp/3426451598249722148</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Flockx</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Contrarian+Thinking</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
